--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0206.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0206.xlsx
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Letters of a Century&lt;/i&gt;</t>
+          <t>&lt;i&gt;Những lá thư của một thế kỷ&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Scissorwoman&lt;/i&gt;</t>
+          <t>&lt;i&gt;Người Phụ Nữ Kéo&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>(&lt;color=RedD&gt;Complete Nutrition Squeezy Jelly is required&lt;/color&gt;)</t>
+          <t>(&lt;color=RedD&gt;Yêu cầu có Thạch Dinh Dưỡng Đầy Đủ&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=yellow&gt;Yellow&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=yellow&gt;Vàng&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Ta không hứng thú.</t>
+          <t>Tao không hứng thú.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Ms. Sugiyama</t>
+          <t>Chị Sugiyama</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Ta muốn kiểm tra mấy công thức nấu ăn.</t>
+          <t>Tao muốn kiểm tra mấy công thức nấu ăn.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Paint...?</t>
+          <t>Tô... Sao?</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Ms. Yuki</t>
+          <t>Cô Yuki</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The Gladiator&lt;/i&gt; Special Issue</t>
+          <t>&lt;i&gt;Ấn phẩm Đặc biệt: &lt;i&gt;Đấu Sĩ&lt;/i&gt;&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Ta sẽ lấy một cái. (Trả 13.500 Tín Dụng Vỏ Sò)</t>
+          <t>Ta sẽ lấy một cái. (Trả 13.500 Shell Credit Sò)</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Ta sẽ lấy một cái. (Trả 9.000 Tín Dụng Vỏ Sò)</t>
+          <t>Ta sẽ lấy một cái. (Trả 9.000 Shell Credit Sò)</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>Gì vậy??</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Prophecy&lt;/i&gt;</t>
+          <t>&lt;i&gt;Lời Tiên Tri&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The Septimont Tribune&lt;/i&gt; Special Issue</t>
+          <t>&lt;i&gt;Tạp Chí Septimont&lt;/i&gt; Số Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=green&gt;Green&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=green&gt;Xanh Lá&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mr. Millkeeper</t>
+          <t>Ông Millkeeper</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=yellow&gt;Yellow&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=yellow&gt;Vàng&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Ta muốn rèn vũ khí.</t>
+          <t>Tao muốn rèn vũ khí.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ta muốn tải lên các Mô-đun.</t>
+          <t>Tao muốn tải lên các Mô-đun.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ta sẽ lấy một cái. (Trả 9.000 Tín Dụng Vỏ Sò)</t>
+          <t>Ta sẽ lấy một cái. (Trả 9.000 Shell Credit Sò)</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>A Diary Không Ký Malee Số 2</t>
+          <t>Nhật Ký Không Ký Tên Số 2</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Ta muốn giao mấy Cỗ Quan Sonance.</t>
+          <t>Tao muốn giao mấy Cỗ Quan Sonance.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>(&lt;color=RedD&gt;Acceptance letter is required&lt;/color&gt;)</t>
+          <t>(&lt;color=RedD&gt;Yêu cầu có Thư Nhập Học&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=blue&gt;Blue&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=blue&gt;Xanh Dương&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Love Rumbles Like a Train&lt;/i&gt;</t>
+          <t>&lt;i&gt;Tình Yêu Rầm Rập Như Đoàn Tàu&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Nhanh lên! Dự Án Công Cụ Hóa Nhiên Liệu F.U.E.L!</t>
+          <t>Tăng tốc nào! Dự án Công Cụ Hóa Nhiên Liệu F.U.E.L.!</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Dr. Collins</t>
+          <t>Tiến sĩ Collins</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Dig!</t>
+          <t>Đào lên nào!</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>(&lt;color=RedD&gt;Dusk Honeypot is required&lt;/color&gt;)</t>
+          <t>(&lt;color=RedD&gt;Yêu cầu có Bình Mật Chạng Vạng&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Đến Nơi End Than Thở&lt;/i&gt;</t>
+          <t>&lt;i&gt;Đến Nơi Kết Thúc Than Thở&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Combat!</t>
+          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Chiến Đấu!</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn gì vậy?</t>
+          <t>Nhìn gì thế?</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>(&lt;color=RedD&gt;Creeping Torchpine cone is required&lt;/color&gt;)</t>
+          <t>(&lt;color=RedD&gt;Yêu cầu có Nón Thông Lửa Leo&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Cần giúp đỡ không?</t>
+          <t>Cần giúp đỡ gì không?</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=red&gt;Red&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=red&gt;Đỏ&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The First Hunter&lt;/i&gt;</t>
+          <t>&lt;i&gt;Thợ Săn Đầu Tiên&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sanhua: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Sanhua: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Baizhi: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Baizhi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Lingyang: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Lingyang: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Lingyang: Hướng dẫn &lt;color=#d4bf5f&gt;Gaining Lion's Spirit&lt;/color&gt;</t>
+          <t>Lingyang: Hướng dẫn &lt;color=#d4bf5f&gt;Thu thập Tinh thần Sư tử&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Chixia: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Chixia: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Encore: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Galbrena Hướng Dẫn &lt;color=#d4bf5f&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt; và Đòn Lao Xuống</t>
+          <t>Galbrena Hướng Dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung - Mưa Tro Tàn Phá&lt;/color&gt; và Đòn Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Galbrena: &lt;color=#d4bf5f&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt; Hướng dẫn Duy Trì Hỏa Lực</t>
+          <t>Galbrena: &lt;color=#d4bf5f&gt;Tấn Công Giữa Không - Ashfall Barrage&lt;/color&gt; Hướng dẫn Duy Trì Hỏa Lực</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Aalto: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Aalto: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Jiyan: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Jiyan: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng dẫn "Lời Kiếm Khắc Bóng Mực"&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Inksplash of Mind&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn "Mực Tâm"&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Undaunted Wayfarer&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng dẫn "Lữ Khách Bất Khuất"&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Verina: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Verina: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Lifethread - Glide&lt;/color&gt; Trên Mặt Đất</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Combo Sợi Sinh Mệnh - Lướt&lt;/color&gt; Trên Mặt Đất</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Lifethread - Glide&lt;/color&gt; Trên Không</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Sợi Sinh Mệnh - Lướt&lt;/color&gt; Trên Không</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Lynae: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt; Hướng Dẫn</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Tấn Công Lao Xuống&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Lynae: Thoát khỏi &lt;color=#d4bf5f&gt;Kaleidoscopic Parade&lt;/color&gt;</t>
+          <t>Lynae: Thoát khỏi &lt;color=#d4bf5f&gt;Diễu Hành Muôn Màu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Taoqi: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Taoqi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Danjin - Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Danjin - Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Rover - Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Vận Mệnh Giả - Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Combo Attack&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Chệch: &lt;color=#d4bf5f&gt;Combo 1&lt;/color&gt;</t>
+          <t>Chệch: &lt;color=#d4bf5f&gt;Hướng dẫn Combo 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Chệch: &lt;color=#d4bf5f&gt;Combo 2&lt;/color&gt;</t>
+          <t>Chệch: &lt;color=#d4bf5f&gt;Hướng dẫn Combo 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Combo 3&lt;/color&gt;</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Combo 3&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Combo 4&lt;/color&gt;</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Combo 4&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Zhezhi triệu hồi &lt;color=Highlight&gt;Inklit Spirit&lt;/color&gt; hỗ trợ chiến đấu.</t>
+          <t>Zhezhi triệu hồi &lt;color=Highlight&gt;Tinh Linh Mực Tím&lt;/color&gt; hỗ trợ chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Youhu: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Youhu: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Chain Mid-air Attack&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Tấn Công Giữa Không Trung Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Vining Waltz&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Vining Waltz&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Vining Waltz&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Vining Waltz&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Mode Switching&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Chuyển Chế Độ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Red Light: Mid-air Attack&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Mid-air Attack (Đèn Đỏ)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Yellow Light: Zoom&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Phóng To (Đèn Vàng)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Necessary Measures&lt;/color&gt;</t>
+          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Biện Pháp Cần Thiết&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt; 1</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt; 2</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt; 3</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt; 3</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Absolution Status&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Combo Trạng Thái Xá Tội&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Confession Status&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Combo Trạng Thái Xưng Tội&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Cantarella: &lt;color=#d4bf5f&gt;Enhanced Mid-air Attack&lt;/color&gt; Phần I</t>
+          <t>Cantarella: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung Nâng Cao&lt;/color&gt; Phần I</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Mid-air Attack&lt;/color&gt; Nâng Cao</t>
+          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Giữa Không II&lt;/color&gt; Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Ngồi xuống và {Cus:Ipt,Touch=tap PC=press Gamepad=press}</t>
+          <t>Ngồi xuống và {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Cartethyia: &lt;color=#d4bf5f&gt;Combo&lt;/color&gt;</t>
+          <t>Cartethyia: &lt;color=#d4bf5f&gt;Hướng dẫn Chuỗi Đòn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Chain Attack&lt;/color&gt;</t>
+          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Mid-air Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Enhanced Mid-air Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không Trung Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} khi vòng tròn trắng xuất hiện.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} khi vòng tròn trắng xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Mid-air Attack&lt;/color&gt;</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Lunar Cycle - Half Moon&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Chu Trình Mặt Trăng - Trăng Khuyết&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Lunar Cycle - New Moon&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Chu kỳ Mặt Trăng - Trăng Non&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Lunar Cycle&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Chu kỳ Mặt Trăng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Mirage&lt;/color&gt;</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18713,7 +18713,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Mirage&lt;/color&gt;</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Mirage&lt;/color&gt;</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở menu Tiện Ích. Di chuột đến &lt;color=#ffd12f&gt;Sensor&lt;/color&gt; và thả ra để chọn</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu Tiện Ích. Di chuột đến &lt;color=#ffd12f&gt;Cảm Biến&lt;/color&gt; và thả ra để chọn</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở menu Tiện Ích. Di chuột đến &lt;color=#ffd12f&gt;Grapple&lt;/color&gt; và thả ra để chọn</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu Tiện Ích. Di chuột đến &lt;color=#ffd12f&gt;Móc Câu&lt;/color&gt; và thả ra để chọn</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Khi Vòng Halo Điểm Yếu xuất hiện, nhấn {0} để &lt;color=#ffd12f&gt;Counterattack&lt;/color&gt;</t>
+          <t>Khi Vòng Halo Điểm Yếu xuất hiện, nhấn {0} để &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Stand cạnh tường và giữ {0} để leo.</t>
+          <t>Đứng cạnh tường và giữ {0} để leo lên.</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Ở thế giới mở có các &lt;color=#ffd12f&gt;Grapple Points&lt;/color&gt;, cậu có thể nhảy xa bằng cách ngắm Móc Treo vào chúng.</t>
+          <t>Ở thế giới mở có các &lt;color=#ffd12f&gt;Điểm Móc Treo&lt;/color&gt;, cậu có thể nhảy xa bằng cách ngắm Móc Treo vào chúng.</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nền tảng thao tác do Học viện Huaxu phát triển, dành cho Cộng Hưởng Giả. Sử dụng để tổng hợp Thuốc Tinh Chế, chế tạo vật phẩm và tinh luyện vật liệu cao cấp.</t>
+          <t>Nền tảng thao tác do Học viện Huaxu phát triển, dành cho Resonator. Sử dụng để tổng hợp Thuốc Tinh Chế, chế tạo vật phẩm và tinh luyện vật liệu cao cấp.</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Hoochief Cyclone có thể tạo ra trường gió hạn chế di chuyển của Cộng Hưởng Giả.</t>
+          <t>Hoochief Cyclone có thể tạo ra trường gió hạn chế di chuyển của Resonator.</t>
         </is>
       </c>
     </row>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Tự Động Hóa Tuần Thám có thể tạo ra bức tường băng để chặn các đòn tấn công tầm xa từ Cộng Hưởng Giả.</t>
+          <t>Tự Động Hóa Tuần Thám có thể tạo ra bức tường băng để chặn các đòn tấn công tầm xa từ Resonator.</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Khi Excarat chui xuống lòng đất, bạn có thể dùng &lt;color=#ffd12f&gt;Plunging Attacks&lt;/color&gt; để buộc nó phải trồi lên.</t>
+          <t>Khi Excarat chui xuống lòng đất, bạn có thể dùng &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; để buộc nó phải trồi lên.</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Đèn Giao Thông có thể khiến Cộng Hưởng Giả rơi vào trạng thái &lt;color=#ffd12f&gt;stagnant&lt;/color&gt;.</t>
+          <t>Đèn Giao Thông có thể khiến Resonator rơi vào trạng thái &lt;color=#ffd12f&gt;trì trệ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Khi Vỏ Sứ Giả Bị Bất Động. Dùng &lt;color=#ffd12f&gt;Hero's Slash&lt;/color&gt; để tiêu diệt nó ngay lập tức.</t>
+          <t>Khi Vỏ Sứ Giả Bị Bất Động. Dùng &lt;color=#ffd12f&gt;Lưỡi Kiếm Anh Hùng&lt;/color&gt; để tiêu diệt nó ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Khi đạt đến một số cấp Liên Minh nhất định, bạn cần hoàn thành &lt;color=#ffd12f&gt;SOL3 Thăng Tiến Pha Quests&lt;/color&gt; để dỡ bỏ &lt;color=#ffd12f&gt;Cấp Liên Minh cap&lt;/color&gt;.</t>
+          <t>Khi đạt đến một số cấp Liên Minh nhất định, bạn cần hoàn thành &lt;color=#ffd12f&gt;Nhiệm Vụ Thăng Hoa Pha SOL3&lt;/color&gt; để dỡ bỏ &lt;color=#ffd12f&gt;giới hạn cấp Liên Minh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Fragile rocks&lt;/color&gt; có thể bị phá hủy bằng các đòn Tấn Công Cơ Bản. Bên trong có thể có thứ gì đó giá trị đấy.</t>
+          <t>&lt;color=#ffd12f&gt;Đá dễ vỡ&lt;/color&gt; có thể bị phá hủy bằng các đòn Basic Attack. Bên trong có thể có thứ gì đó giá trị đấy.</t>
         </is>
       </c>
     </row>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Khi Cộng Hưởng Giả đang ở trạng thái &lt;color=#ffd12f&gt;Mô-đun: Speed&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;launched&lt;/color&gt; theo hướng mũi tên.</t>
+          <t>Khi Resonator đang ở trạng thái &lt;color=#ffd12f&gt;Mô-đun: Tốc Độ&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;bắn đi&lt;/color&gt; theo hướng mũi tên.</t>
         </is>
       </c>
     </row>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Khi Cộng Hưởng Giả nhảy lên &lt;color=#ffd12f&gt;Mô-đun: Nhảy&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;bounced&lt;/color&gt; phía trên.</t>
+          <t>Khi Resonator nhảy lên &lt;color=#ffd12f&gt;Mô-đun: Nhảy&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;nảy lên&lt;/color&gt; phía trên.</t>
         </is>
       </c>
     </row>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Khi Cộng Hưởng Giả nhảy lên &lt;color=#ffd12f&gt;Flobble&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;bounced&lt;/color&gt; phía trên.</t>
+          <t>Khi Resonator nhảy lên &lt;color=#ffd12f&gt;Flobble&lt;/color&gt;, họ sẽ bị &lt;color=#ffd12f&gt;nảy lên&lt;/color&gt; phía trên.</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Sau khi lướt qua &lt;color=#ffd12f&gt;Gravitation Vortex Ring&lt;/color&gt;, cậu sẽ nhận được &lt;color=#ffd12f&gt;acceleration&lt;/color&gt; theo hướng chỉ định.</t>
+          <t>Sau khi lướt qua &lt;color=#ffd12f&gt;Vòng Xoáy Trọng Lực&lt;/color&gt;, cậu sẽ nhận được &lt;color=#ffd12f&gt;gia tốc&lt;/color&gt; theo hướng chỉ định.</t>
         </is>
       </c>
     </row>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;Spinning&lt;/color&gt; để &lt;color=#ffd12f&gt;connect pathways&lt;/color&gt; và hoàn tất truyền tải thông tin.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;Thiết Bị Xoay&lt;/color&gt; để &lt;color=#ffd12f&gt;kết nối các đường dẫn&lt;/color&gt; và hoàn tất truyền tải thông tin.</t>
         </is>
       </c>
     </row>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tiếng vọng có khả năng Biến Hình trong Khu Triển Khai có thể được kéo thẳng vào Khu Biến Hình để kích hoạt. Tiếng vọng được sử dụng theo cách này cũng sẽ bị tiêu hao.</t>
+          <t>Echo có khả năng Biến Hình trong Khu Triển Khai có thể được kéo thẳng vào Khu Biến Hình để kích hoạt. Echo được sử dụng theo cách này cũng sẽ bị tiêu hao.</t>
         </is>
       </c>
     </row>
@@ -22879,7 +22879,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Đội Comp Tutorial (Demo):&lt;/color&gt;</t>
+          <t>&lt;color=yellow&gt;Hướng dẫn đội hình (Demo): &lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonator Introduction:&lt;/color&gt;</t>
+          <t>&lt;color=yellow&gt;Giới thiệu Resonator: &lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23208,7 +23208,7 @@
       <c r="M350" t="inlineStr">
         <is>
           <t>["Chi Tiết Sự Kiện"]
-Sau khi hoàn thành Tháp Nghịch Cảnh: Vùng Ổn Định &amp; Vùng Thí Nghiệm, bạn có thể nhận Cộng Hưởng Giả "Yuanwu" cùng các phần thưởng khác.</t>
+Sau khi hoàn thành Tháp Nghịch Cảnh: Vùng Ổn Định &amp; Vùng Thí Nghiệm, bạn có thể nhận Resonator "Yuanwu" cùng các phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Character Introduction:&lt;/color&gt;</t>
+          <t>&lt;color=yellow&gt;Giới Thiệu Nhân Vật: &lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Dùng thành phần để &lt;color=#ffd12f&gt;fill&lt;/color&gt; &lt;color=#ffd12f&gt;highlighted area&lt;/color&gt; trong ma trận và kích hoạt nó.</t>
+          <t>Dùng thành phần để &lt;color=#ffd12f&gt;lấp đầy&lt;/color&gt; &lt;color=#ffd12f&gt;vùng sáng&lt;/color&gt; trong ma trận và kích hoạt nó.</t>
         </is>
       </c>
     </row>
@@ -23403,7 +23403,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=#ffd12f&gt;Detonate&lt;/color&gt; gần &lt;color=#ffd12f&gt;Explosive Charge&lt;/color&gt; để đốt cháy và &lt;color=#ffd12f&gt;destroy&lt;/color&gt; nó.</t>
+          <t>Kích hoạt &lt;color=#ffd12f&gt;Điện Nổ&lt;/color&gt; gần &lt;color=#ffd12f&gt;Bẫy Gai&lt;/color&gt; để đốt cháy và &lt;color=#ffd12f&gt;phá hủy&lt;/color&gt; nó.</t>
         </is>
       </c>
     </row>
@@ -23468,7 +23468,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -23533,7 +23533,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -23663,7 +23663,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -24120,7 +24120,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Rover. Giữ {0} để giải phóng sức mạnh.</t>
+          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Vận Mệnh Giả. Giữ {0} để giải phóng sức mạnh.</t>
         </is>
       </c>
     </row>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Rover. Giữ {0} để giải phóng sức mạnh.</t>
+          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Vận Mệnh Giả. Giữ {0} để giải phóng sức mạnh.</t>
         </is>
       </c>
     </row>
@@ -24315,7 +24315,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Những bức tường đổ nát và đống gạch vụn nằm la liệt khắp Khu Tàn Tích Lơ Lửng. Hãy dùng &lt;color=#ffd12f&gt;Pull&lt;/color&gt; để điều khiển hoặc phá hủy những chướng ngại vật này.</t>
+          <t>Những bức tường đổ nát và đống gạch vụn nằm la liệt khắp Khu Tàn Tích Lơ Lửng. Hãy dùng &lt;color=#ffd12f&gt;Kéo&lt;/color&gt; để điều khiển hoặc phá hủy những chướng ngại vật này.</t>
         </is>
       </c>
     </row>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Quests&lt;/color&gt; qua vòng điều hướng và xem các nhiệm vụ hiện tại</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Nhiệm Vụ&lt;/color&gt; qua vòng điều hướng và xem các nhiệm vụ hiện tại</t>
         </is>
       </c>
     </row>
@@ -24575,7 +24575,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Nhấn {0} để sử dụng &lt;color=#ffd12f&gt;Grapple&lt;/color&gt;</t>
+          <t>Nhấn {0} để sử dụng &lt;color=#ffd12f&gt;Móc Câu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24770,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Nhấn {0} giữa không trung để thực hiện &lt;color=#ffd12f&gt;backflip&lt;/color&gt;.</t>
+          <t>Nhấn {0} giữa không trung để thực hiện &lt;color=#ffd12f&gt;lộn ngược&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24900,7 +24900,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng và chuyển đổi &lt;color=#ffd12f&gt;Attribute&lt;/color&gt; của Rover</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng và chuyển đổi &lt;color=#ffd12f&gt;Thuộc Tính&lt;/color&gt; của Rover</t>
         </is>
       </c>
     </row>
@@ -24965,7 +24965,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng và chuyển đổi &lt;color=#ffd12f&gt;Attribute&lt;/color&gt; của Rover</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng và chuyển đổi &lt;color=#ffd12f&gt;Thuộc Tính&lt;/color&gt; của Rover</t>
         </is>
       </c>
     </row>
@@ -25030,7 +25030,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Tương tác với công tắc để điều chỉnh vị trí của &lt;color=#ffd12f&gt;Holographic Baffle&lt;/color&gt;, tạo ra &lt;color=#ffd12f&gt;different pathway&lt;/color&gt;.</t>
+          <t>Tương tác với công tắc để điều chỉnh vị trí của &lt;color=#ffd12f&gt;Rào Cản Hologram&lt;/color&gt;, tạo ra &lt;color=#ffd12f&gt;lối đi khác&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Nhấn &lt;color=#ffd12f&gt;Aim&lt;/color&gt; để ngắm bắn</t>
+          <t>Nhấn &lt;color=#ffd12f&gt;Ngắm&lt;/color&gt; để ngắm bắn</t>
         </is>
       </c>
     </row>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Đã nhận vũ khí mới. Giữ &lt;color=#ffd12f&gt;Press and hold&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Resonators&lt;/color&gt; qua bánh xe lệnh.</t>
+          <t>Đã nhận vũ khí mới. Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua bánh xe lệnh.</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
       <c r="M387" t="inlineStr">
         <is>
           <t>Biến hình thành Clang Bang và lấp đầy khối băng còn thiếu để hoàn thành thử thách.
-Hãy chắc chắn &lt;color=#ffd12f&gt;face the right direction&lt;/color&gt;.</t>
+Hãy chắc chắn &lt;color=#ffd12f&gt;hướng đúng phía&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25682,7 +25682,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tương tác với máy móc để bắt đầu Thử Thách Tiếng Vang: Clang Bang và biến hình thành Clang Bang.</t>
+          <t>Tương tác với máy móc để bắt đầu Thử Thách Echo: Clang Bang và biến hình thành Clang Bang.</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Biến hình thành Clang Bang và dùng &lt;color=#ffd12f&gt;Leap Device&lt;/color&gt; phóng mình vào &lt;color=#ffd12f&gt;Ice Walls&lt;/color&gt; để phá vỡ nó.</t>
+          <t>Biến hình thành Clang Bang và dùng &lt;color=#ffd12f&gt;Thiết bị Nhảy&lt;/color&gt; phóng mình vào &lt;color=#ffd12f&gt;Bức tường Băng&lt;/color&gt; để phá vỡ nó.</t>
         </is>
       </c>
     </row>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Thiết bị tiếp nhận ánh sáng sẽ kích hoạt sau khi được chiếu sáng &lt;color=#ffd12f&gt;continuously&lt;/color&gt; bởi Light Emitter trong một khoảng thời gian nhất định.</t>
+          <t>Thiết bị tiếp nhận ánh sáng sẽ kích hoạt sau khi được chiếu sáng &lt;color=#ffd12f&gt;liên tục&lt;/color&gt; bởi Light Emitter trong một khoảng thời gian nhất định.</t>
         </is>
       </c>
     </row>
@@ -26007,7 +26007,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;Pressure Platform&lt;/color&gt; gần đó để nâng hoặc hạ cột đá.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;Bệ Nén Áp Lực&lt;/color&gt; gần đó để nâng hoặc hạ cột đá.</t>
         </is>
       </c>
     </row>
@@ -26267,7 +26267,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Dùng {0} để bắn với Hoverdroid: Shooter.</t>
+          <t>Dùng {0} để khai hỏa với Hoverdroid: Shooter.</t>
         </is>
       </c>
     </row>
@@ -26462,7 +26462,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn combo &lt;color=#d4bf5f&gt;Mid-air Sickle Attack&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn combo &lt;color=#d4bf5f&gt;Đòn Hái Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26527,7 +26527,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn combo &lt;color=#d4bf5f&gt;Mid-air Scythe Attack&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn combo &lt;color=#d4bf5f&gt;Đòn Liềm Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Dodge&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Né Tránh Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26722,7 +26722,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Rune: Trust&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Rune: Tin Tưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26852,7 +26852,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Rune: Answer&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Rune: Đáp Lời&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26917,7 +26917,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Rune: Trust &amp; Answer&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Rune: Tin Tưởng &amp; Đáp Lời&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Two Runes: Trust&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Hai Rune: Tin Tưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#ffd12f&gt;Plunging Attacks&lt;/color&gt; để đánh vào cơ chế dưới đất và khớp mẫu với thiết kế trên tường.</t>
+          <t>Sử dụng &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; để đánh vào cơ chế dưới đất và khớp mẫu với thiết kế trên tường.</t>
         </is>
       </c>
     </row>
@@ -28347,7 +28347,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Trong lúc lướt đi, hãy cố tránh những &lt;color=#ffd12f&gt;red rings&lt;/color&gt;.</t>
+          <t>Trong lúc lướt đi, hãy cố tránh những &lt;color=#ffd12f&gt;vòng tròn đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Rào cản sẽ chặn Cộng Hưởng Giả và các vật phẩm khác, nhưng xung năng lượng của KU-Key vẫn có thể xuyên qua.</t>
+          <t>Rào cản sẽ chặn Resonator và các vật phẩm khác, nhưng xung năng lượng của KU-Key vẫn có thể xuyên qua.</t>
         </is>
       </c>
     </row>
@@ -28674,7 +28674,7 @@
       <c r="M434" t="inlineStr">
         <is>
           <t>["Trang Phục"]
-Trang Phục là ngoại hình thay thế cho Cộng Hưởng Giả có thể chơi được. Một số Trang Phục đi kèm với Hình Chiếu Vũ Khí đặc biệt, có thể thay đổi ngoại hình vũ khí.</t>
+Trang Phục là ngoại hình thay thế cho Resonator có thể chơi được. Một số Trang Phục đi kèm với Hình Chiếu Vũ Khí đặc biệt, có thể thay đổi ngoại hình vũ khí.</t>
         </is>
       </c>
     </row>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Người Gác Bờ sẽ tăng cường các đòn Tấn Công Cơ Bản của cậu.</t>
+          <t>Người Gác Bờ sẽ tăng cường các đòn Basic Attack của cậu.</t>
         </is>
       </c>
     </row>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Người Gác Bờ sẽ tăng cường các đòn Tấn Công Cơ Bản của cậu.</t>
+          <t>Người Gác Bờ sẽ tăng cường các đòn Basic Attack của cậu.</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Người Gác Bờ sẽ tăng cường các đòn Tấn Công Cơ Bản của cậu.</t>
+          <t>Người Gác Bờ sẽ tăng cường các đòn Basic Attack của cậu.</t>
         </is>
       </c>
     </row>
@@ -29519,7 +29519,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt;</t>
+          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Lao Xuống&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29584,7 +29584,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Sync Strike&lt;/color&gt;</t>
+          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Đồng Bộ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Sync Attack&lt;/color&gt;</t>
+          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Đồng Bộ Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Plunging Attack&lt;/color&gt; (Dạng Cơ Giới)</t>
+          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Đòn Lao Xuống&lt;/color&gt; (Dạng Cơ Giới)</t>
         </is>
       </c>
     </row>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Sync Strike&lt;/color&gt; (Dạng Cơ Giới)</t>
+          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Đòn Đồng Bộ&lt;/color&gt; (Dạng Cơ Giới)</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29844,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Enhanced Sync Attack&lt;/color&gt; (Dạng Cơ Giới)</t>
+          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Đòn Đồng Bộ Tăng Cường&lt;/color&gt; (Dạng Cơ Giới)</t>
         </is>
       </c>
     </row>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Aemeath: &lt;color=#d4bf5f&gt;Sync Strike&lt;/color&gt;</t>
+          <t>Aemeath: &lt;color=#d4bf5f&gt;Hướng dẫn Combo Đồng Bộ Tấn Công&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Mid-air Attack - Present Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn - Tấn Công Giữa Không - Bản Ngã Hiện Tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30039,7 +30039,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Foreclaiming: Inward Vision&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Tiên Định: Nội Quan&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30104,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Mid-air Attack - Foreclaimed Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn - Tấn Công Giữa Không - Bản Ngã Đã Định&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Foreclaiming: Blade Liberation&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Tiên Định: Giải Phóng Kiếm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30234,7 +30234,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Mid-air Attack - Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Giữa Không - Hình Thức Stagecraft&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30299,7 +30299,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;stick&lt;/color&gt; và nút &lt;color=#ffd12f&gt;Dodge&lt;/color&gt; để bắt đầu chạy nước rút</t>
+          <t>Giữ &lt;color=#ffd12f&gt;que điều khiển&lt;/color&gt; và nút &lt;color=#ffd12f&gt;Né Tránh&lt;/color&gt; để bắt đầu chạy nước rút</t>
         </is>
       </c>
     </row>
@@ -30364,7 +30364,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Nhấn nút khi &lt;color=#ffd12f&gt;frequency signal&lt;/color&gt; chạm đến &lt;color=#ffd12f&gt;designated area&lt;/color&gt;.</t>
+          <t>Nhấn nút khi &lt;color=#ffd12f&gt;tín hiệu tần số&lt;/color&gt; chạm đến &lt;color=#ffd12f&gt;vùng chỉ định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Giữ {0} để điều khiển KU-Key và xóa tham nhũng.</t>
+          <t>Giữ {0} để điều khiển KU-Key và thanh tẩy sự ô uế.</t>
         </is>
       </c>
     </row>
@@ -31471,7 +31471,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Rương Biến Hình có thể bị đánh bại ngay lập tức bằng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;.</t>
+          <t>Rương Biến Hình có thể bị đánh bại ngay lập tức bằng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Lorelei triệu hồi những quả cầu nước đặc biệt lơ lửng về phía cô. Những quả cầu này sẽ ban phát hiệu ứng tăng cường khi được Lorelei hoặc Cộng Hưởng Giả đang hoạt động hấp thụ.</t>
+          <t>Lorelei triệu hồi những quả cầu nước đặc biệt lơ lửng về phía cô. Những quả cầu này sẽ ban phát hiệu ứng tăng cường khi được Lorelei hoặc Resonator đang hoạt động hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -31666,7 +31666,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Roi của Hecate chính là phần mở rộng của bản thân cô ấy và có thể bị chặn lại bằng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;.</t>
+          <t>Roi của Hecate chính là phần mở rộng của bản thân cô ấy và có thể bị chặn lại bằng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31928,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi điều khiển Gondola ở chế độ Chơi Đơn, bạn có thể mở menu Chia Sẻ Hành Trình bằng cách nhấn vào &lt;color=#ffd12f&gt;Cruise Share button&lt;/color&gt;.</t>
+          <t>Khi điều khiển Gondola ở chế độ Chơi Đơn, bạn có thể mở menu Chia Sẻ Hành Trình bằng cách nhấn vào &lt;color=#ffd12f&gt;nút Chia Sẻ Hành Trình&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31993,7 +31993,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Trong menu Cruise Share, Rover có thể mời &lt;color=#ffd12f&gt;an obtained Resonator&lt;/color&gt; cùng đi Gondola.</t>
+          <t>Trong menu Cruise Share, Rover có thể mời &lt;color=#ffd12f&gt;một Resonator đã sở hữu&lt;/color&gt; cùng đi Gondola.</t>
         </is>
       </c>
     </row>
@@ -32188,7 +32188,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Bay theo Dấu Gió cho phép bạn &lt;color=#ffd12f&gt;automatically&lt;/color&gt; di chuyển theo hướng gió.</t>
+          <t>Bay theo Dấu Gió cho phép bạn &lt;color=#ffd12f&gt;tự động&lt;/color&gt; di chuyển theo hướng gió.</t>
         </is>
       </c>
     </row>
